--- a/mapping/Vertebrate_Other.xlsx
+++ b/mapping/Vertebrate_Other.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B304"/>
+  <dimension ref="A1:B335"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -520,7 +520,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>大麻哈鱼属</t>
+          <t>钩吻鲑属</t>
         </is>
       </c>
     </row>
@@ -1192,7 +1192,7 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>九刺鱼属</t>
+          <t>刺鱼属</t>
         </is>
       </c>
     </row>
@@ -1336,7 +1336,7 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>夜鹰属（美夜鹰属）</t>
+          <t>夜鹰属</t>
         </is>
       </c>
     </row>
@@ -1372,7 +1372,7 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>斑马鱼属</t>
+          <t>䰾属</t>
         </is>
       </c>
     </row>
@@ -1528,7 +1528,7 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>胡子鲶属</t>
+          <t>胡鲇属</t>
         </is>
       </c>
     </row>
@@ -1552,7 +1552,7 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>尼柯巴鸠属</t>
+          <t>紫巾鸠属</t>
         </is>
       </c>
     </row>
@@ -1852,7 +1852,7 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>地雀鹀属</t>
+          <t>地雀属</t>
         </is>
       </c>
     </row>
@@ -1960,7 +1960,7 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>合附蟾属</t>
+          <t>铃蟾属</t>
         </is>
       </c>
     </row>
@@ -2572,7 +2572,7 @@
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>吸汁啄木鸟属</t>
+          <t>啄木鸟属</t>
         </is>
       </c>
     </row>
@@ -2920,7 +2920,7 @@
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>扁背龟属</t>
+          <t>潮龟属</t>
         </is>
       </c>
     </row>
@@ -3304,7 +3304,7 @@
       </c>
       <c r="B241" t="inlineStr">
         <is>
-          <t>星蜂鸟属</t>
+          <t>蜂鸟属</t>
         </is>
       </c>
     </row>
@@ -3568,7 +3568,7 @@
       </c>
       <c r="B263" t="inlineStr">
         <is>
-          <t>拟水龟属</t>
+          <t>乌龟属</t>
         </is>
       </c>
     </row>
@@ -3580,7 +3580,7 @@
       </c>
       <c r="B264" t="inlineStr">
         <is>
-          <t>棱皮龟属</t>
+          <t>革龟属</t>
         </is>
       </c>
     </row>
@@ -3904,7 +3904,7 @@
       </c>
       <c r="B291" t="inlineStr">
         <is>
-          <t>雨滨蛙属</t>
+          <t>树蟾属</t>
         </is>
       </c>
     </row>
@@ -3928,7 +3928,7 @@
       </c>
       <c r="B293" t="inlineStr">
         <is>
-          <t>胎生蜥蜴属</t>
+          <t>胎生蜥属</t>
         </is>
       </c>
     </row>
@@ -3964,7 +3964,7 @@
       </c>
       <c r="B296" t="inlineStr">
         <is>
-          <t>帆鳍鱼属</t>
+          <t>古鲈属</t>
         </is>
       </c>
     </row>
@@ -4019,48 +4019,420 @@
     <row r="301">
       <c r="A301" t="inlineStr">
         <is>
-          <t>Larus</t>
+          <t>Eurypyga</t>
         </is>
       </c>
       <c r="B301" t="inlineStr">
         <is>
-          <t>鸥属</t>
+          <t>日鳽属</t>
         </is>
       </c>
     </row>
     <row r="302">
       <c r="A302" t="inlineStr">
         <is>
-          <t>Myiozetetes</t>
+          <t>Lonchura</t>
         </is>
       </c>
       <c r="B302" t="inlineStr">
         <is>
-          <t>蝇霸鹟属</t>
+          <t>文鸟属</t>
         </is>
       </c>
     </row>
     <row r="303">
       <c r="A303" t="inlineStr">
         <is>
-          <t>Cuculus</t>
+          <t>Calidris</t>
         </is>
       </c>
       <c r="B303" t="inlineStr">
         <is>
-          <t>杜鹃属</t>
+          <t>滨鹬属</t>
         </is>
       </c>
     </row>
     <row r="304">
       <c r="A304" t="inlineStr">
         <is>
+          <t>Indicator</t>
+        </is>
+      </c>
+      <c r="B304" t="inlineStr">
+        <is>
+          <t>响蜜䴕属</t>
+        </is>
+      </c>
+    </row>
+    <row r="305">
+      <c r="A305" t="inlineStr">
+        <is>
+          <t>Phaethon</t>
+        </is>
+      </c>
+      <c r="B305" t="inlineStr">
+        <is>
+          <t>鹲属</t>
+        </is>
+      </c>
+    </row>
+    <row r="306">
+      <c r="A306" t="inlineStr">
+        <is>
+          <t>Apus</t>
+        </is>
+      </c>
+      <c r="B306" t="inlineStr">
+        <is>
+          <t>雨燕属</t>
+        </is>
+      </c>
+    </row>
+    <row r="307">
+      <c r="A307" t="inlineStr">
+        <is>
+          <t>Charadrius</t>
+        </is>
+      </c>
+      <c r="B307" t="inlineStr">
+        <is>
+          <t>鸻属</t>
+        </is>
+      </c>
+    </row>
+    <row r="308">
+      <c r="A308" t="inlineStr">
+        <is>
+          <t>Pithys</t>
+        </is>
+      </c>
+      <c r="B308" t="inlineStr">
+        <is>
+          <t>白顶蚁鸟属</t>
+        </is>
+      </c>
+    </row>
+    <row r="309">
+      <c r="A309" t="inlineStr">
+        <is>
+          <t>Gymnogyps</t>
+        </is>
+      </c>
+      <c r="B309" t="inlineStr">
+        <is>
+          <t>加州神鹫属</t>
+        </is>
+      </c>
+    </row>
+    <row r="310">
+      <c r="A310" t="inlineStr">
+        <is>
+          <t>Cariama</t>
+        </is>
+      </c>
+      <c r="B310" t="inlineStr">
+        <is>
+          <t>叫鹤属</t>
+        </is>
+      </c>
+    </row>
+    <row r="311">
+      <c r="A311" t="inlineStr">
+        <is>
+          <t>Larus</t>
+        </is>
+      </c>
+      <c r="B311" t="inlineStr">
+        <is>
+          <t>鸥属</t>
+        </is>
+      </c>
+    </row>
+    <row r="312">
+      <c r="A312" t="inlineStr">
+        <is>
+          <t>Cuculus</t>
+        </is>
+      </c>
+      <c r="B312" t="inlineStr">
+        <is>
+          <t>杜鹃属</t>
+        </is>
+      </c>
+    </row>
+    <row r="313">
+      <c r="A313" t="inlineStr">
+        <is>
+          <t>Dunckerocampus</t>
+        </is>
+      </c>
+      <c r="B313" t="inlineStr">
+        <is>
+          <t>邓克氏海龙属</t>
+        </is>
+      </c>
+    </row>
+    <row r="314">
+      <c r="A314" t="inlineStr">
+        <is>
+          <t>Tauraco</t>
+        </is>
+      </c>
+      <c r="B314" t="inlineStr">
+        <is>
+          <t>蕉鹃属</t>
+        </is>
+      </c>
+    </row>
+    <row r="315">
+      <c r="A315" t="inlineStr">
+        <is>
+          <t>Nestor</t>
+        </is>
+      </c>
+      <c r="B315" t="inlineStr">
+        <is>
+          <t>啄羊鹦鹉属</t>
+        </is>
+      </c>
+    </row>
+    <row r="316">
+      <c r="A316" t="inlineStr">
+        <is>
+          <t>Sylvia</t>
+        </is>
+      </c>
+      <c r="B316" t="inlineStr">
+        <is>
+          <t>林莺属</t>
+        </is>
+      </c>
+    </row>
+    <row r="317">
+      <c r="A317" t="inlineStr">
+        <is>
+          <t>Neopsephotus</t>
+        </is>
+      </c>
+      <c r="B317" t="inlineStr">
+        <is>
+          <t>红腰鹦鹉属</t>
+        </is>
+      </c>
+    </row>
+    <row r="318">
+      <c r="A318" t="inlineStr">
+        <is>
+          <t>Motacilla</t>
+        </is>
+      </c>
+      <c r="B318" t="inlineStr">
+        <is>
+          <t>鹡鸰属</t>
+        </is>
+      </c>
+    </row>
+    <row r="319">
+      <c r="A319" t="inlineStr">
+        <is>
+          <t>Strigops</t>
+        </is>
+      </c>
+      <c r="B319" t="inlineStr">
+        <is>
+          <t>鸮鹦鹉属</t>
+        </is>
+      </c>
+    </row>
+    <row r="320">
+      <c r="A320" t="inlineStr">
+        <is>
+          <t>Myiozetetes</t>
+        </is>
+      </c>
+      <c r="B320" t="inlineStr">
+        <is>
+          <t>霸鹟属</t>
+        </is>
+      </c>
+    </row>
+    <row r="321">
+      <c r="A321" t="inlineStr">
+        <is>
+          <t>Chlamydotis</t>
+        </is>
+      </c>
+      <c r="B321" t="inlineStr">
+        <is>
+          <t>波斑鸨属</t>
+        </is>
+      </c>
+    </row>
+    <row r="322">
+      <c r="A322" t="inlineStr">
+        <is>
+          <t>Leptosomus</t>
+        </is>
+      </c>
+      <c r="B322" t="inlineStr">
+        <is>
+          <t>鹃鴗属</t>
+        </is>
+      </c>
+    </row>
+    <row r="323">
+      <c r="A323" t="inlineStr">
+        <is>
           <t>Serinus</t>
         </is>
       </c>
-      <c r="B304" t="inlineStr">
+      <c r="B323" t="inlineStr">
         <is>
           <t>丝雀属</t>
+        </is>
+      </c>
+    </row>
+    <row r="324">
+      <c r="A324" t="inlineStr">
+        <is>
+          <t>Pyxicephalus</t>
+        </is>
+      </c>
+      <c r="B324" t="inlineStr">
+        <is>
+          <t>箱头蛙属</t>
+        </is>
+      </c>
+    </row>
+    <row r="325">
+      <c r="A325" t="inlineStr">
+        <is>
+          <t>Fulmarus</t>
+        </is>
+      </c>
+      <c r="B325" t="inlineStr">
+        <is>
+          <t>暴风鹱属</t>
+        </is>
+      </c>
+    </row>
+    <row r="326">
+      <c r="A326" t="inlineStr">
+        <is>
+          <t>Varanus</t>
+        </is>
+      </c>
+      <c r="B326" t="inlineStr">
+        <is>
+          <t>巨蜥属</t>
+        </is>
+      </c>
+    </row>
+    <row r="327">
+      <c r="A327" t="inlineStr">
+        <is>
+          <t>Pempheris</t>
+        </is>
+      </c>
+      <c r="B327" t="inlineStr">
+        <is>
+          <t>单鳍鱼属</t>
+        </is>
+      </c>
+    </row>
+    <row r="328">
+      <c r="A328" t="inlineStr">
+        <is>
+          <t>Lates</t>
+        </is>
+      </c>
+      <c r="B328" t="inlineStr">
+        <is>
+          <t>尖吻鲈属</t>
+        </is>
+      </c>
+    </row>
+    <row r="329">
+      <c r="A329" t="inlineStr">
+        <is>
+          <t>Hirundo</t>
+        </is>
+      </c>
+      <c r="B329" t="inlineStr">
+        <is>
+          <t>燕属</t>
+        </is>
+      </c>
+    </row>
+    <row r="330">
+      <c r="A330" t="inlineStr">
+        <is>
+          <t>Scophthalmus</t>
+        </is>
+      </c>
+      <c r="B330" t="inlineStr">
+        <is>
+          <t>菱鲆属</t>
+        </is>
+      </c>
+    </row>
+    <row r="331">
+      <c r="A331" t="inlineStr">
+        <is>
+          <t>Empidonax</t>
+        </is>
+      </c>
+      <c r="B331" t="inlineStr">
+        <is>
+          <t>纹霸鹟属</t>
+        </is>
+      </c>
+    </row>
+    <row r="332">
+      <c r="A332" t="inlineStr">
+        <is>
+          <t>Apaloderma</t>
+        </is>
+      </c>
+      <c r="B332" t="inlineStr">
+        <is>
+          <t>咬鹃属</t>
+        </is>
+      </c>
+    </row>
+    <row r="333">
+      <c r="A333" t="inlineStr">
+        <is>
+          <t>Acanthisitta</t>
+        </is>
+      </c>
+      <c r="B333" t="inlineStr">
+        <is>
+          <t>刺鹩属</t>
+        </is>
+      </c>
+    </row>
+    <row r="334">
+      <c r="A334" t="inlineStr">
+        <is>
+          <t>Buceros</t>
+        </is>
+      </c>
+      <c r="B334" t="inlineStr">
+        <is>
+          <t>犀鸟属</t>
+        </is>
+      </c>
+    </row>
+    <row r="335">
+      <c r="A335" t="inlineStr">
+        <is>
+          <t>Pterocles</t>
+        </is>
+      </c>
+      <c r="B335" t="inlineStr">
+        <is>
+          <t>沙鸡属</t>
         </is>
       </c>
     </row>
